--- a/Excel/TalentConfig.xlsx
+++ b/Excel/TalentConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -84,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="120">
   <si>
     <t>ID</t>
   </si>
@@ -441,6 +446,9 @@
   </si>
   <si>
     <t>提高道伤倍率{0}%</t>
+  </si>
+  <si>
+    <t>#</t>
   </si>
 </sst>
 </file>
@@ -1417,7 +1425,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S92"/>
+  <dimension ref="A1:S117"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="4" customWidth="1"/>
@@ -4266,7 +4274,7 @@
         <v>301</v>
       </c>
       <c r="D69" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>41</v>
@@ -4310,7 +4318,7 @@
         <v>302</v>
       </c>
       <c r="D70" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>111</v>
@@ -4354,7 +4362,7 @@
         <v>303</v>
       </c>
       <c r="D71" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>45</v>
@@ -4398,7 +4406,7 @@
         <v>304</v>
       </c>
       <c r="D72" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>113</v>
@@ -4443,7 +4451,7 @@
         <v>305</v>
       </c>
       <c r="D73" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>115</v>
@@ -4488,7 +4496,7 @@
         <v>306</v>
       </c>
       <c r="D74" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>117</v>
@@ -4533,7 +4541,7 @@
         <v>307</v>
       </c>
       <c r="D75" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>57</v>
@@ -4578,7 +4586,7 @@
         <v>308</v>
       </c>
       <c r="D76" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>59</v>
@@ -4623,7 +4631,7 @@
         <v>309</v>
       </c>
       <c r="D77" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>61</v>
@@ -4668,7 +4676,7 @@
         <v>310</v>
       </c>
       <c r="D78" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>63</v>
@@ -4713,7 +4721,7 @@
         <v>311</v>
       </c>
       <c r="D79" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>66</v>
@@ -4758,7 +4766,7 @@
         <v>312</v>
       </c>
       <c r="D80" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>69</v>
@@ -4798,12 +4806,12 @@
         <v>71</v>
       </c>
     </row>
-    <row r="81" customHeight="1" spans="3:16">
+    <row r="81" customHeight="1" spans="1:16">
       <c r="C81" s="2">
         <v>313</v>
       </c>
-      <c r="D81" s="3">
-        <v>2</v>
+      <c r="D81" s="2">
+        <v>4</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>41</v>
@@ -4843,12 +4851,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="82" customHeight="1" spans="3:16">
+    <row r="82" customHeight="1" spans="1:16">
       <c r="C82" s="2">
         <v>314</v>
       </c>
       <c r="D82" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>111</v>
@@ -4888,12 +4896,12 @@
         <v>112</v>
       </c>
     </row>
-    <row r="83" customHeight="1" spans="3:16">
+    <row r="83" customHeight="1" spans="1:16">
       <c r="C83" s="2">
         <v>315</v>
       </c>
       <c r="D83" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>45</v>
@@ -4933,12 +4941,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="84" customHeight="1" spans="3:16">
+    <row r="84" customHeight="1" spans="1:16">
       <c r="C84" s="2">
         <v>316</v>
       </c>
       <c r="D84" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>113</v>
@@ -4978,12 +4986,12 @@
         <v>114</v>
       </c>
     </row>
-    <row r="85" customHeight="1" spans="3:16">
+    <row r="85" customHeight="1" spans="1:16">
       <c r="C85" s="2">
         <v>317</v>
       </c>
       <c r="D85" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>115</v>
@@ -5023,12 +5031,12 @@
         <v>116</v>
       </c>
     </row>
-    <row r="86" customHeight="1" spans="3:16">
+    <row r="86" customHeight="1" spans="1:16">
       <c r="C86" s="2">
         <v>318</v>
       </c>
       <c r="D86" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>117</v>
@@ -5068,12 +5076,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="87" customHeight="1" spans="3:16">
+    <row r="87" customHeight="1" spans="1:16">
       <c r="C87" s="2">
         <v>319</v>
       </c>
       <c r="D87" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>57</v>
@@ -5113,12 +5121,12 @@
         <v>58</v>
       </c>
     </row>
-    <row r="88" customHeight="1" spans="3:16">
+    <row r="88" customHeight="1" spans="1:16">
       <c r="C88" s="2">
         <v>320</v>
       </c>
       <c r="D88" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>59</v>
@@ -5158,12 +5166,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="89" customHeight="1" spans="3:16">
+    <row r="89" customHeight="1" spans="1:16">
       <c r="C89" s="2">
         <v>321</v>
       </c>
       <c r="D89" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>61</v>
@@ -5203,12 +5211,12 @@
         <v>62</v>
       </c>
     </row>
-    <row r="90" customHeight="1" spans="3:16">
+    <row r="90" customHeight="1" spans="1:16">
       <c r="C90" s="2">
         <v>322</v>
       </c>
       <c r="D90" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>63</v>
@@ -5248,12 +5256,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="91" customHeight="1" spans="3:16">
+    <row r="91" customHeight="1" spans="1:16">
       <c r="C91" s="2">
         <v>323</v>
       </c>
       <c r="D91" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>66</v>
@@ -5293,12 +5301,12 @@
         <v>68</v>
       </c>
     </row>
-    <row r="92" customHeight="1" spans="3:16">
+    <row r="92" customHeight="1" spans="1:16">
       <c r="C92" s="2">
         <v>324</v>
       </c>
       <c r="D92" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>69</v>
@@ -5335,6 +5343,1227 @@
         <v>6</v>
       </c>
       <c r="P92" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="94" customHeight="1" spans="1:16">
+      <c r="A94" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C94" s="2">
+        <v>401</v>
+      </c>
+      <c r="D94" s="2">
+        <v>5</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G94" s="2">
+        <v>0</v>
+      </c>
+      <c r="H94" s="2">
+        <v>290</v>
+      </c>
+      <c r="I94" s="2">
+        <v>20</v>
+      </c>
+      <c r="J94" s="2">
+        <v>2003</v>
+      </c>
+      <c r="K94" s="2">
+        <v>50</v>
+      </c>
+      <c r="L94" s="2">
+        <v>1</v>
+      </c>
+      <c r="M94" s="2">
+        <v>50</v>
+      </c>
+      <c r="N94" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O94" s="2">
+        <v>2</v>
+      </c>
+      <c r="P94" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="95" customHeight="1" spans="1:16">
+      <c r="A95" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C95" s="2">
+        <v>402</v>
+      </c>
+      <c r="D95" s="2">
+        <v>5</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G95" s="2">
+        <v>0</v>
+      </c>
+      <c r="H95" s="2">
+        <v>290</v>
+      </c>
+      <c r="I95" s="2">
+        <v>20</v>
+      </c>
+      <c r="J95" s="2">
+        <v>2013</v>
+      </c>
+      <c r="K95" s="2">
+        <v>20</v>
+      </c>
+      <c r="L95" s="2">
+        <v>1</v>
+      </c>
+      <c r="M95" s="2">
+        <v>20</v>
+      </c>
+      <c r="N95" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O95" s="2">
+        <v>2</v>
+      </c>
+      <c r="P95" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" spans="1:16">
+      <c r="A96" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C96" s="2">
+        <v>403</v>
+      </c>
+      <c r="D96" s="2">
+        <v>5</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G96" s="2">
+        <v>0</v>
+      </c>
+      <c r="H96" s="2">
+        <v>290</v>
+      </c>
+      <c r="I96" s="2">
+        <v>20</v>
+      </c>
+      <c r="J96" s="2">
+        <v>2012</v>
+      </c>
+      <c r="K96" s="2">
+        <v>50</v>
+      </c>
+      <c r="L96" s="2">
+        <v>1</v>
+      </c>
+      <c r="M96" s="2">
+        <v>50</v>
+      </c>
+      <c r="N96" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O96" s="2">
+        <v>2</v>
+      </c>
+      <c r="P96" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="1:16">
+      <c r="A97" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C97" s="2">
+        <v>404</v>
+      </c>
+      <c r="D97" s="2">
+        <v>5</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G97" s="2">
+        <v>0</v>
+      </c>
+      <c r="H97" s="2">
+        <f t="shared" ref="H97:H105" si="5">H94+20</f>
+        <v>310</v>
+      </c>
+      <c r="I97" s="2">
+        <v>20</v>
+      </c>
+      <c r="J97" s="2">
+        <v>2007</v>
+      </c>
+      <c r="K97" s="2">
+        <v>20</v>
+      </c>
+      <c r="L97" s="2">
+        <v>1</v>
+      </c>
+      <c r="M97" s="2">
+        <v>20</v>
+      </c>
+      <c r="N97" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O97" s="2">
+        <v>2</v>
+      </c>
+      <c r="P97" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="98" customHeight="1" spans="1:16">
+      <c r="A98" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C98" s="2">
+        <v>405</v>
+      </c>
+      <c r="D98" s="2">
+        <v>5</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G98" s="2">
+        <v>0</v>
+      </c>
+      <c r="H98" s="2">
+        <f t="shared" si="5"/>
+        <v>310</v>
+      </c>
+      <c r="I98" s="2">
+        <v>20</v>
+      </c>
+      <c r="J98" s="2">
+        <v>2008</v>
+      </c>
+      <c r="K98" s="2">
+        <v>20</v>
+      </c>
+      <c r="L98" s="2">
+        <v>1</v>
+      </c>
+      <c r="M98" s="2">
+        <v>20</v>
+      </c>
+      <c r="N98" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O98" s="2">
+        <v>2</v>
+      </c>
+      <c r="P98" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="1:16">
+      <c r="A99" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C99" s="2">
+        <v>406</v>
+      </c>
+      <c r="D99" s="2">
+        <v>5</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G99" s="2">
+        <v>0</v>
+      </c>
+      <c r="H99" s="2">
+        <f t="shared" si="5"/>
+        <v>310</v>
+      </c>
+      <c r="I99" s="2">
+        <v>20</v>
+      </c>
+      <c r="J99" s="2">
+        <v>2009</v>
+      </c>
+      <c r="K99" s="2">
+        <v>20</v>
+      </c>
+      <c r="L99" s="2">
+        <v>1</v>
+      </c>
+      <c r="M99" s="2">
+        <v>20</v>
+      </c>
+      <c r="N99" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O99" s="2">
+        <v>2</v>
+      </c>
+      <c r="P99" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="1:16">
+      <c r="A100" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C100" s="2">
+        <v>407</v>
+      </c>
+      <c r="D100" s="2">
+        <v>5</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G100" s="2">
+        <v>0</v>
+      </c>
+      <c r="H100" s="2">
+        <f t="shared" si="5"/>
+        <v>330</v>
+      </c>
+      <c r="I100" s="2">
+        <v>20</v>
+      </c>
+      <c r="J100" s="2">
+        <v>32</v>
+      </c>
+      <c r="K100" s="2">
+        <v>2</v>
+      </c>
+      <c r="L100" s="2">
+        <v>1</v>
+      </c>
+      <c r="M100" s="2">
+        <v>2</v>
+      </c>
+      <c r="N100" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O100" s="2">
+        <v>4</v>
+      </c>
+      <c r="P100" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="1:16">
+      <c r="A101" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C101" s="2">
+        <v>408</v>
+      </c>
+      <c r="D101" s="2">
+        <v>5</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G101" s="2">
+        <v>0</v>
+      </c>
+      <c r="H101" s="2">
+        <f t="shared" si="5"/>
+        <v>330</v>
+      </c>
+      <c r="I101" s="2">
+        <v>20</v>
+      </c>
+      <c r="J101" s="2">
+        <v>2001</v>
+      </c>
+      <c r="K101" s="2">
+        <v>20</v>
+      </c>
+      <c r="L101" s="2">
+        <v>1</v>
+      </c>
+      <c r="M101" s="2">
+        <v>20</v>
+      </c>
+      <c r="N101" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O101" s="2">
+        <v>4</v>
+      </c>
+      <c r="P101" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" spans="1:16">
+      <c r="A102" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C102" s="2">
+        <v>409</v>
+      </c>
+      <c r="D102" s="2">
+        <v>5</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G102" s="2">
+        <v>0</v>
+      </c>
+      <c r="H102" s="2">
+        <f t="shared" si="5"/>
+        <v>330</v>
+      </c>
+      <c r="I102" s="2">
+        <v>20</v>
+      </c>
+      <c r="J102" s="2">
+        <v>31</v>
+      </c>
+      <c r="K102" s="2">
+        <v>2</v>
+      </c>
+      <c r="L102" s="2">
+        <v>1</v>
+      </c>
+      <c r="M102" s="2">
+        <v>2</v>
+      </c>
+      <c r="N102" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O102" s="2">
+        <v>4</v>
+      </c>
+      <c r="P102" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" spans="1:16">
+      <c r="A103" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C103" s="2">
+        <v>410</v>
+      </c>
+      <c r="D103" s="2">
+        <v>5</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G103" s="2">
+        <v>0</v>
+      </c>
+      <c r="H103" s="2">
+        <f t="shared" si="5"/>
+        <v>350</v>
+      </c>
+      <c r="I103" s="2">
+        <v>10</v>
+      </c>
+      <c r="J103" s="2">
+        <v>93</v>
+      </c>
+      <c r="K103" s="2">
+        <v>2</v>
+      </c>
+      <c r="L103" s="2">
+        <v>1</v>
+      </c>
+      <c r="M103" s="2">
+        <v>2</v>
+      </c>
+      <c r="N103" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O103" s="2">
+        <v>6</v>
+      </c>
+      <c r="P103" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="104" customHeight="1" spans="1:16">
+      <c r="A104" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C104" s="2">
+        <v>411</v>
+      </c>
+      <c r="D104" s="2">
+        <v>5</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G104" s="2">
+        <v>0</v>
+      </c>
+      <c r="H104" s="2">
+        <f t="shared" si="5"/>
+        <v>350</v>
+      </c>
+      <c r="I104" s="2">
+        <v>10</v>
+      </c>
+      <c r="J104" s="2">
+        <v>91</v>
+      </c>
+      <c r="K104" s="2">
+        <v>2</v>
+      </c>
+      <c r="L104" s="2">
+        <v>1</v>
+      </c>
+      <c r="M104" s="2">
+        <v>2</v>
+      </c>
+      <c r="N104" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O104" s="2">
+        <v>6</v>
+      </c>
+      <c r="P104" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" spans="1:16">
+      <c r="A105" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C105" s="2">
+        <v>412</v>
+      </c>
+      <c r="D105" s="2">
+        <v>5</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G105" s="2">
+        <v>0</v>
+      </c>
+      <c r="H105" s="2">
+        <f t="shared" si="5"/>
+        <v>350</v>
+      </c>
+      <c r="I105" s="2">
+        <v>10</v>
+      </c>
+      <c r="J105" s="2">
+        <v>92</v>
+      </c>
+      <c r="K105" s="2">
+        <v>2</v>
+      </c>
+      <c r="L105" s="2">
+        <v>1</v>
+      </c>
+      <c r="M105" s="2">
+        <v>2</v>
+      </c>
+      <c r="N105" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O105" s="2">
+        <v>6</v>
+      </c>
+      <c r="P105" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="1:16">
+      <c r="A106" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C106" s="2">
+        <v>413</v>
+      </c>
+      <c r="D106" s="2">
+        <v>5</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G106" s="2">
+        <v>0</v>
+      </c>
+      <c r="H106" s="2">
+        <f t="shared" ref="H106:H117" si="6">H81+100</f>
+        <v>470</v>
+      </c>
+      <c r="I106" s="2">
+        <v>20</v>
+      </c>
+      <c r="J106" s="2">
+        <v>2003</v>
+      </c>
+      <c r="K106" s="2">
+        <v>50</v>
+      </c>
+      <c r="L106" s="2">
+        <v>1</v>
+      </c>
+      <c r="M106" s="2">
+        <v>50</v>
+      </c>
+      <c r="N106" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O106" s="2">
+        <v>2</v>
+      </c>
+      <c r="P106" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" spans="1:16">
+      <c r="A107" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C107" s="2">
+        <v>414</v>
+      </c>
+      <c r="D107" s="2">
+        <v>5</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G107" s="2">
+        <v>0</v>
+      </c>
+      <c r="H107" s="2">
+        <f t="shared" si="6"/>
+        <v>470</v>
+      </c>
+      <c r="I107" s="2">
+        <v>20</v>
+      </c>
+      <c r="J107" s="2">
+        <v>2013</v>
+      </c>
+      <c r="K107" s="2">
+        <v>20</v>
+      </c>
+      <c r="L107" s="2">
+        <v>1</v>
+      </c>
+      <c r="M107" s="2">
+        <v>20</v>
+      </c>
+      <c r="N107" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O107" s="2">
+        <v>2</v>
+      </c>
+      <c r="P107" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="108" customHeight="1" spans="1:16">
+      <c r="A108" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C108" s="2">
+        <v>415</v>
+      </c>
+      <c r="D108" s="2">
+        <v>5</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G108" s="2">
+        <v>0</v>
+      </c>
+      <c r="H108" s="2">
+        <f t="shared" si="6"/>
+        <v>470</v>
+      </c>
+      <c r="I108" s="2">
+        <v>20</v>
+      </c>
+      <c r="J108" s="2">
+        <v>2012</v>
+      </c>
+      <c r="K108" s="2">
+        <v>50</v>
+      </c>
+      <c r="L108" s="2">
+        <v>1</v>
+      </c>
+      <c r="M108" s="2">
+        <v>50</v>
+      </c>
+      <c r="N108" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O108" s="2">
+        <v>2</v>
+      </c>
+      <c r="P108" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="109" customHeight="1" spans="1:16">
+      <c r="A109" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C109" s="2">
+        <v>416</v>
+      </c>
+      <c r="D109" s="2">
+        <v>5</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G109" s="2">
+        <v>0</v>
+      </c>
+      <c r="H109" s="2">
+        <f t="shared" si="6"/>
+        <v>490</v>
+      </c>
+      <c r="I109" s="2">
+        <v>20</v>
+      </c>
+      <c r="J109" s="2">
+        <v>2007</v>
+      </c>
+      <c r="K109" s="2">
+        <v>20</v>
+      </c>
+      <c r="L109" s="2">
+        <v>1</v>
+      </c>
+      <c r="M109" s="2">
+        <v>20</v>
+      </c>
+      <c r="N109" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O109" s="2">
+        <v>2</v>
+      </c>
+      <c r="P109" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="110" customHeight="1" spans="1:16">
+      <c r="A110" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C110" s="2">
+        <v>417</v>
+      </c>
+      <c r="D110" s="2">
+        <v>5</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G110" s="2">
+        <v>0</v>
+      </c>
+      <c r="H110" s="2">
+        <f t="shared" si="6"/>
+        <v>490</v>
+      </c>
+      <c r="I110" s="2">
+        <v>20</v>
+      </c>
+      <c r="J110" s="2">
+        <v>2008</v>
+      </c>
+      <c r="K110" s="2">
+        <v>20</v>
+      </c>
+      <c r="L110" s="2">
+        <v>1</v>
+      </c>
+      <c r="M110" s="2">
+        <v>20</v>
+      </c>
+      <c r="N110" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O110" s="2">
+        <v>2</v>
+      </c>
+      <c r="P110" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="111" customHeight="1" spans="1:16">
+      <c r="A111" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C111" s="2">
+        <v>418</v>
+      </c>
+      <c r="D111" s="2">
+        <v>5</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G111" s="2">
+        <v>0</v>
+      </c>
+      <c r="H111" s="2">
+        <f t="shared" si="6"/>
+        <v>490</v>
+      </c>
+      <c r="I111" s="2">
+        <v>20</v>
+      </c>
+      <c r="J111" s="2">
+        <v>2009</v>
+      </c>
+      <c r="K111" s="2">
+        <v>20</v>
+      </c>
+      <c r="L111" s="2">
+        <v>1</v>
+      </c>
+      <c r="M111" s="2">
+        <v>20</v>
+      </c>
+      <c r="N111" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O111" s="2">
+        <v>2</v>
+      </c>
+      <c r="P111" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="112" customHeight="1" spans="1:16">
+      <c r="A112" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C112" s="2">
+        <v>419</v>
+      </c>
+      <c r="D112" s="2">
+        <v>5</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G112" s="2">
+        <v>0</v>
+      </c>
+      <c r="H112" s="2">
+        <f t="shared" si="6"/>
+        <v>510</v>
+      </c>
+      <c r="I112" s="2">
+        <v>20</v>
+      </c>
+      <c r="J112" s="2">
+        <v>32</v>
+      </c>
+      <c r="K112" s="2">
+        <v>2</v>
+      </c>
+      <c r="L112" s="2">
+        <v>1</v>
+      </c>
+      <c r="M112" s="2">
+        <v>2</v>
+      </c>
+      <c r="N112" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O112" s="2">
+        <v>4</v>
+      </c>
+      <c r="P112" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="113" customHeight="1" spans="1:16">
+      <c r="A113" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C113" s="2">
+        <v>420</v>
+      </c>
+      <c r="D113" s="2">
+        <v>5</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G113" s="2">
+        <v>0</v>
+      </c>
+      <c r="H113" s="2">
+        <f t="shared" si="6"/>
+        <v>510</v>
+      </c>
+      <c r="I113" s="2">
+        <v>20</v>
+      </c>
+      <c r="J113" s="2">
+        <v>2001</v>
+      </c>
+      <c r="K113" s="2">
+        <v>20</v>
+      </c>
+      <c r="L113" s="2">
+        <v>1</v>
+      </c>
+      <c r="M113" s="2">
+        <v>20</v>
+      </c>
+      <c r="N113" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O113" s="2">
+        <v>4</v>
+      </c>
+      <c r="P113" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="114" customHeight="1" spans="1:16">
+      <c r="A114" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C114" s="2">
+        <v>421</v>
+      </c>
+      <c r="D114" s="2">
+        <v>5</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G114" s="2">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2">
+        <f t="shared" si="6"/>
+        <v>510</v>
+      </c>
+      <c r="I114" s="2">
+        <v>20</v>
+      </c>
+      <c r="J114" s="2">
+        <v>31</v>
+      </c>
+      <c r="K114" s="2">
+        <v>2</v>
+      </c>
+      <c r="L114" s="2">
+        <v>1</v>
+      </c>
+      <c r="M114" s="2">
+        <v>2</v>
+      </c>
+      <c r="N114" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O114" s="2">
+        <v>4</v>
+      </c>
+      <c r="P114" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="115" customHeight="1" spans="1:16">
+      <c r="A115" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C115" s="2">
+        <v>422</v>
+      </c>
+      <c r="D115" s="2">
+        <v>5</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G115" s="2">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2">
+        <f t="shared" si="6"/>
+        <v>530</v>
+      </c>
+      <c r="I115" s="2">
+        <v>10</v>
+      </c>
+      <c r="J115" s="2">
+        <v>93</v>
+      </c>
+      <c r="K115" s="2">
+        <v>2</v>
+      </c>
+      <c r="L115" s="2">
+        <v>1</v>
+      </c>
+      <c r="M115" s="2">
+        <v>2</v>
+      </c>
+      <c r="N115" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O115" s="2">
+        <v>6</v>
+      </c>
+      <c r="P115" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" spans="1:16">
+      <c r="A116" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C116" s="2">
+        <v>423</v>
+      </c>
+      <c r="D116" s="2">
+        <v>5</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G116" s="2">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2">
+        <f t="shared" si="6"/>
+        <v>530</v>
+      </c>
+      <c r="I116" s="2">
+        <v>10</v>
+      </c>
+      <c r="J116" s="2">
+        <v>91</v>
+      </c>
+      <c r="K116" s="2">
+        <v>2</v>
+      </c>
+      <c r="L116" s="2">
+        <v>1</v>
+      </c>
+      <c r="M116" s="2">
+        <v>2</v>
+      </c>
+      <c r="N116" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O116" s="2">
+        <v>6</v>
+      </c>
+      <c r="P116" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" spans="1:16">
+      <c r="A117" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C117" s="2">
+        <v>424</v>
+      </c>
+      <c r="D117" s="2">
+        <v>5</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G117" s="2">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2">
+        <f t="shared" si="6"/>
+        <v>530</v>
+      </c>
+      <c r="I117" s="2">
+        <v>10</v>
+      </c>
+      <c r="J117" s="2">
+        <v>92</v>
+      </c>
+      <c r="K117" s="2">
+        <v>2</v>
+      </c>
+      <c r="L117" s="2">
+        <v>1</v>
+      </c>
+      <c r="M117" s="2">
+        <v>2</v>
+      </c>
+      <c r="N117" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O117" s="2">
+        <v>6</v>
+      </c>
+      <c r="P117" s="2" t="s">
         <v>71</v>
       </c>
     </row>
